--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1195,6 +1195,200 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128862498</v>
+      </c>
+      <c r="B6" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>522182</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7036575</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128862499</v>
+      </c>
+      <c r="B7" t="n">
+        <v>100807</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>522176</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7036627</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100807</v>
+        <v>100813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100839</v>
+        <v>100844</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100844</v>
+        <v>100847</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100847</v>
+        <v>100857</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100857</v>
+        <v>100864</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100864</v>
+        <v>100866</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100866</v>
+        <v>100892</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100892</v>
+        <v>100894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100894</v>
+        <v>100895</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -1201,7 +1201,7 @@
         <v>128862498</v>
       </c>
       <c r="B6" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1298,7 +1298,7 @@
         <v>128862499</v>
       </c>
       <c r="B7" t="n">
-        <v>100895</v>
+        <v>100899</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89046630</v>
+        <v>89046629</v>
       </c>
       <c r="B2" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97358</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>53</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>521970.9954412825</v>
+        <v>522139</v>
       </c>
       <c r="R2" t="n">
-        <v>7036526.85297217</v>
+        <v>7036499</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -774,7 +759,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>äldre granskog</t>
+          <t>gammal granskog med rikört</t>
         </is>
       </c>
       <c r="AN2" t="n">
@@ -782,7 +767,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov granlåga, förrötad</t>
+          <t>1 substratenheter # grov asplåga</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -804,15 +789,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89046635</v>
+        <v>89046634</v>
       </c>
       <c r="B3" t="n">
-        <v>89673</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87196</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -820,34 +800,43 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>427</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Puderspindling</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Cortinarius aureopulverulentus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>522042.1423509059</v>
+        <v>521982</v>
       </c>
       <c r="R3" t="n">
-        <v>7036537.184116861</v>
+        <v>7036453</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -877,21 +866,11 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -903,15 +882,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>olikåldrig gammal granskog</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
+          <t>svagt kalkpåverkad, ca 140-årig granskog</t>
+        </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>1 substratenheter # grov granlåga, förrötad</t>
+          <t>i komposterad barrmatta i kanten av aktiv myrstack</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -933,15 +909,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>89046636</v>
+        <v>89046630</v>
       </c>
       <c r="B4" t="n">
-        <v>86210</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -949,43 +920,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4412</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Äggvaxskivling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hygrophorus karstenii</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sacc. &amp; Cub.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>522092.1288912459</v>
+        <v>521971</v>
       </c>
       <c r="R4" t="n">
-        <v>7036627.884898427</v>
+        <v>7036527</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1015,21 +977,11 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1041,7 +993,15 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>mossig, ca 140-årig granskog</t>
+          <t>äldre granskog</t>
+        </is>
+      </c>
+      <c r="AN4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>1 substratenheter # grov granlåga, förrötad</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1063,15 +1023,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>89046634</v>
+        <v>89046635</v>
       </c>
       <c r="B5" t="n">
-        <v>85129</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1079,43 +1034,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>427</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Puderspindling</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cortinarius aureopulverulentus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>521981.8049930805</v>
+        <v>522042</v>
       </c>
       <c r="R5" t="n">
-        <v>7036453.120156074</v>
+        <v>7036537</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1145,21 +1091,11 @@
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2020-09-15</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1171,12 +1107,15 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>svagt kalkpåverkad, ca 140-årig granskog</t>
-        </is>
+          <t>olikåldrig gammal granskog</t>
+        </is>
+      </c>
+      <c r="AN5" t="n">
+        <v>1</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>i komposterad barrmatta i kanten av aktiv myrstack</t>
+          <t>1 substratenheter # grov granlåga, förrötad</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1198,45 +1137,54 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128862498</v>
+        <v>89046636</v>
       </c>
       <c r="B6" t="n">
-        <v>100899</v>
+        <v>89156</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>4412</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Äggvaxskivling</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hygrophorus karstenii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>Sacc. &amp; Cub.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>522182</v>
+        <v>522092</v>
       </c>
       <c r="R6" t="n">
-        <v>7036575</v>
+        <v>7036628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1263,12 +1211,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1279,61 +1227,70 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>mossig, ca 140-årig granskog</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128862499</v>
+        <v>89046631</v>
       </c>
       <c r="B7" t="n">
-        <v>100899</v>
+        <v>79413</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>222498</v>
+        <v>6450</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Skuggblåslav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hypogymnia vittata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Ach.) Parrique</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ruven, Jmt</t>
+          <t>Skårelflyn, V om, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>522176</v>
+        <v>521946</v>
       </c>
       <c r="R7" t="n">
-        <v>7036627</v>
+        <v>7036442</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1360,12 +1317,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2020-09-15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,19 +1333,227 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>olikåldrig granskog med fräken och lågörtsfläckar på svagt fuktig mark</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>nordvänd lodyta på stort block</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128862498</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>522182</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7036575</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>Benny Öwre</t>
         </is>
       </c>
-      <c r="AY7" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128862499</v>
+      </c>
+      <c r="B9" t="n">
+        <v>101325</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ruven, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>522176</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7036627</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Hammerdal</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Benny Öwre</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27624-2025 artfynd.xlsx
+++ b/artfynd/A 27624-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -906,6 +916,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046634</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1020,6 +1035,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046630</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046635</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046636</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1360,6 +1390,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89046631</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1457,6 +1492,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862498</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1554,8 +1594,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128862499</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>